--- a/CHARMS BEADS DISNEY.xlsx
+++ b/CHARMS BEADS DISNEY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95F677D9-1DB8-4361-B0CE-AE017723F453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A88BC1A-FA65-4A0A-823A-21A7A0959CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0A3D0F50-D46A-4AA3-8C9D-74D0C1C259E3}"/>
   </bookViews>
@@ -12371,7 +12371,9 @@
       </c>
       <c r="I2" s="10"/>
       <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
+      <c r="K2" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
@@ -12397,10 +12399,10 @@
         <v>70</v>
       </c>
       <c r="I3" s="10"/>
-      <c r="J3" s="10">
+      <c r="J3" s="10"/>
+      <c r="K3" s="10">
         <v>1</v>
       </c>
-      <c r="K3" s="10"/>
     </row>
     <row r="4" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
@@ -12426,9 +12428,7 @@
         <v>75</v>
       </c>
       <c r="I4" s="10"/>
-      <c r="J4" s="10">
-        <v>1</v>
-      </c>
+      <c r="J4" s="10"/>
       <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -12455,10 +12455,10 @@
         <v>65</v>
       </c>
       <c r="I5" s="10"/>
-      <c r="J5" s="10">
+      <c r="J5" s="10"/>
+      <c r="K5" s="10">
         <v>1</v>
       </c>
-      <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
@@ -12483,11 +12483,11 @@
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10">
         <v>1</v>
       </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
@@ -12512,11 +12512,11 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10">
         <v>1</v>
       </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
@@ -12541,11 +12541,11 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10">
         <v>1</v>
       </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
@@ -12570,11 +12570,11 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10">
         <v>1</v>
       </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
@@ -12600,10 +12600,10 @@
         <v>70</v>
       </c>
       <c r="I10" s="10"/>
-      <c r="J10" s="10">
+      <c r="J10" s="10"/>
+      <c r="K10" s="10">
         <v>1</v>
       </c>
-      <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
@@ -12629,9 +12629,7 @@
         <v>65</v>
       </c>
       <c r="I11" s="10"/>
-      <c r="J11" s="10">
-        <v>1</v>
-      </c>
+      <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -12658,10 +12656,10 @@
         <v>70</v>
       </c>
       <c r="I12" s="10"/>
-      <c r="J12" s="10">
+      <c r="J12" s="10"/>
+      <c r="K12" s="10">
         <v>1</v>
       </c>
-      <c r="K12" s="10"/>
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -12797,7 +12795,9 @@
       </c>
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="K17" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
@@ -13042,9 +13042,7 @@
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
-      <c r="K26" s="10">
-        <v>1</v>
-      </c>
+      <c r="K26" s="10"/>
     </row>
     <row r="27" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
@@ -13368,11 +13366,11 @@
         <f t="shared" si="2"/>
         <v>65</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10">
         <v>1</v>
       </c>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
     </row>
     <row r="39" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
@@ -13397,9 +13395,7 @@
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="I39" s="10">
-        <v>1</v>
-      </c>
+      <c r="I39" s="10"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
     </row>
@@ -13588,11 +13584,11 @@
         <f t="shared" si="2"/>
         <v>65</v>
       </c>
-      <c r="I46" s="10">
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10">
         <v>1</v>
       </c>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
     </row>
     <row r="47" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
@@ -19302,18 +19298,18 @@
         <v>0</v>
       </c>
       <c r="D258" s="9">
-        <f t="shared" ref="D258:D321" si="12">(C258*8)+3</f>
+        <f t="shared" ref="D258:D274" si="12">(C258*8)+3</f>
         <v>3</v>
       </c>
       <c r="E258" s="9">
-        <f t="shared" ref="E258:E321" si="13">D258*2</f>
+        <f t="shared" ref="E258:E274" si="13">D258*2</f>
         <v>6</v>
       </c>
       <c r="F258" s="9">
         <v>55</v>
       </c>
       <c r="G258" s="9">
-        <f t="shared" ref="G258:G321" si="14">F258+10</f>
+        <f t="shared" ref="G258:G274" si="14">F258+10</f>
         <v>65</v>
       </c>
       <c r="I258" s="10"/>

--- a/CHARMS BEADS DISNEY.xlsx
+++ b/CHARMS BEADS DISNEY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A88BC1A-FA65-4A0A-823A-21A7A0959CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22438471-0991-476D-B68F-6C258CF1FE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0A3D0F50-D46A-4AA3-8C9D-74D0C1C259E3}"/>
   </bookViews>
@@ -12466,22 +12466,22 @@
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="8">
-        <v>3.42</v>
+        <v>3.16</v>
       </c>
       <c r="D6" s="9">
         <f t="shared" si="0"/>
-        <v>30.36</v>
+        <v>28.28</v>
       </c>
       <c r="E6" s="9">
         <f t="shared" si="1"/>
-        <v>60.72</v>
+        <v>56.56</v>
       </c>
       <c r="F6" s="9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" si="2"/>
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>

--- a/CHARMS BEADS DISNEY.xlsx
+++ b/CHARMS BEADS DISNEY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22438471-0991-476D-B68F-6C258CF1FE3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC442C9-F75E-492C-BA60-7418B09E08BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0A3D0F50-D46A-4AA3-8C9D-74D0C1C259E3}"/>
   </bookViews>
@@ -13069,9 +13069,7 @@
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="10"/>
-      <c r="K27" s="10">
-        <v>1</v>
-      </c>
+      <c r="K27" s="10"/>
     </row>
     <row r="28" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
